--- a/test_results_fold_final.xlsx
+++ b/test_results_fold_final.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4948852062225342</v>
+        <v>0.4463377594947815</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5336915850639343</v>
+        <v>0.5405266880989075</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5275444388389587</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4818158745765686</v>
+        <v>0.5619257092475891</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4857808351516724</v>
+        <v>0.3688849210739136</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4877139925956726</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4977322816848755</v>
+        <v>0.9012587070465088</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5318257808685303</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5347992181777954</v>
+        <v>0.952199399471283</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5287755131721497</v>
+        <v>0.4219536781311035</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4990813732147217</v>
+        <v>0.2181929349899292</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4919329881668091</v>
+        <v>0.9981664419174194</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5081470012664795</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5069898962974548</v>
+        <v>0.4809615612030029</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4949897527694702</v>
+        <v>0.3341734409332275</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4946594834327698</v>
+        <v>0.3811160326004028</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5187822580337524</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5239918828010559</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5202792286872864</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5178496241569519</v>
+        <v>0.999998927116394</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5254797339439392</v>
+        <v>0.9941529631614685</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.49651038646698</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5142818093299866</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4898505210876465</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4953051805496216</v>
+        <v>0.9828136563301086</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5347006916999817</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5187838077545166</v>
+        <v>0.9999919533729553</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.516329824924469</v>
+        <v>0.9992778897285461</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5075228810310364</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5022367238998413</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5280149579048157</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.488713800907135</v>
+        <v>0.9314654469490051</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5173318982124329</v>
+        <v>0.2773913145065308</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4860967993736267</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5318402051925659</v>
+        <v>0.7922338843345642</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5409732460975647</v>
+        <v>0.416485071182251</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5166239738464355</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4994522333145142</v>
+        <v>0.2447982430458069</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4918296337127686</v>
+        <v>0.2497549057006836</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5094115734100342</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5117726922035217</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5085798501968384</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5029810070991516</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5185428261756897</v>
+        <v>0.4229689836502075</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5097160935401917</v>
+        <v>0.6193885207176208</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5351382493972778</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5485162734985352</v>
+        <v>0.2698744535446167</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5139452219009399</v>
+        <v>0.9973993301391602</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4933241009712219</v>
+        <v>0.4170030355453491</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5148977637290955</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5169566869735718</v>
+        <v>0.4872182607650757</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5038274526596069</v>
+        <v>0.5513115525245667</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5095701813697815</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5422280430793762</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.502662181854248</v>
+        <v>0.9943369626998901</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4981251955032349</v>
+        <v>0.9995725154876709</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5170864462852478</v>
+        <v>0.5494782328605652</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5249800682067871</v>
+        <v>0.9779792428016663</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5088056921958923</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5305773019790649</v>
+        <v>0.3122338652610779</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5482768416404724</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5317026972770691</v>
+        <v>0.6037106513977051</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4935692548751831</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.5264554023742676</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5392001271247864</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4997819662094116</v>
+        <v>0.3947950601577759</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5141498446464539</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.4948424696922302</v>
+        <v>0.9999989867210388</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5116450786590576</v>
+        <v>0.4845213294029236</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5418121218681335</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.5016543865203857</v>
+        <v>0.9999973177909851</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4975066184997559</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4938347339630127</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4949907064437866</v>
+        <v>0.6628864407539368</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4765982627868652</v>
+        <v>0.2342692613601685</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4995653629302979</v>
+        <v>0.4125577211380005</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5091049671173096</v>
+        <v>0.5538498163223267</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5250301957130432</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.5046947598457336</v>
+        <v>0.4972222447395325</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.5247373580932617</v>
+        <v>0.9999465346336365</v>
       </c>
     </row>
   </sheetData>

--- a/test_results_fold_final.xlsx
+++ b/test_results_fold_final.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4463377594947815</v>
+        <v>0.7111018896102905</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5405266880989075</v>
+        <v>0.844275176525116</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.9589231014251709</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5619257092475891</v>
+        <v>0.8794415593147278</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3688849210739136</v>
+        <v>0.7167659401893616</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9999999403953552</v>
+        <v>0.8766928911209106</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9012587070465088</v>
+        <v>0.8241267204284668</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9675952196121216</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.952199399471283</v>
+        <v>0.8840601444244385</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4219536781311035</v>
+        <v>0.69524747133255</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2181929349899292</v>
+        <v>0.6372659802436829</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9981664419174194</v>
+        <v>0.3926773071289062</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0.7630854249000549</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4809615612030029</v>
+        <v>0.9689931273460388</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3341734409332275</v>
+        <v>0.4610260128974915</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3811160326004028</v>
+        <v>0.6163369417190552</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.9678318500518799</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.9514259696006775</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9999999403953552</v>
+        <v>0.8544203042984009</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.999998927116394</v>
+        <v>0.7304010391235352</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9941529631614685</v>
+        <v>0.9329248070716858</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.9661262035369873</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.9529105424880981</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0.9044431447982788</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9828136563301086</v>
+        <v>0.2565562725067139</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.9708537459373474</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9999919533729553</v>
+        <v>0.9649748802185059</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9992778897285461</v>
+        <v>0.7420475482940674</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.9048248529434204</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0.9289169311523438</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0.9621776342391968</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9314654469490051</v>
+        <v>0.5780013799667358</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2773913145065308</v>
+        <v>0.2739785313606262</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0.8898189067840576</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7922338843345642</v>
+        <v>0.9259671568870544</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.416485071182251</v>
+        <v>0.6748971939086914</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0.8376629948616028</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2447982430458069</v>
+        <v>0.1708706617355347</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2497549057006836</v>
+        <v>0.7072519063949585</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0.5471808314323425</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9999999403953552</v>
+        <v>0.8551753163337708</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0.8712447285652161</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0.8935849666595459</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4229689836502075</v>
+        <v>0.6667560338973999</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6193885207176208</v>
+        <v>0.7963299155235291</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0.953804075717926</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2698744535446167</v>
+        <v>0.632418155670166</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9973993301391602</v>
+        <v>0.8907746076583862</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4170030355453491</v>
+        <v>0.02012646198272705</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0.9103339910507202</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4872182607650757</v>
+        <v>0.6842058300971985</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5513115525245667</v>
+        <v>0.6369934678077698</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>0.1455458402633667</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0.9293562173843384</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9943369626998901</v>
+        <v>0.445898175239563</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9995725154876709</v>
+        <v>0.5845574736595154</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5494782328605652</v>
+        <v>0.7140905261039734</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9779792428016663</v>
+        <v>0.1577112078666687</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0.964714527130127</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3122338652610779</v>
+        <v>0.3050634860992432</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0.9094895720481873</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6037106513977051</v>
+        <v>0.5194316506385803</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0.7728552222251892</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0.9517062306404114</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0.9554732441902161</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3947950601577759</v>
+        <v>0.8298839926719666</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0.8261349201202393</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9999989867210388</v>
+        <v>0.8332823514938354</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4845213294029236</v>
+        <v>0.8657451272010803</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0.9411430954933167</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9999973177909851</v>
+        <v>0.9257025718688965</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0.9287473559379578</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>0.4325308799743652</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6628864407539368</v>
+        <v>0.4400296211242676</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2342692613601685</v>
+        <v>0.6069982051849365</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4125577211380005</v>
+        <v>0.1380116939544678</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5538498163223267</v>
+        <v>0.4111279845237732</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0.9539011716842651</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4972222447395325</v>
+        <v>0.7279855012893677</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9999465346336365</v>
+        <v>0.8164682388305664</v>
       </c>
     </row>
   </sheetData>

--- a/test_results_fold_final.xlsx
+++ b/test_results_fold_final.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7111018896102905</v>
+        <v>0.5391277670860291</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.844275176525116</v>
+        <v>0.6076937317848206</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9589231014251709</v>
+        <v>0.9999997019767761</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8794415593147278</v>
+        <v>0.8661360740661621</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7167659401893616</v>
+        <v>0.9997403621673584</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8766928911209106</v>
+        <v>0.9859791994094849</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8241267204284668</v>
+        <v>0.9996679425239563</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9675952196121216</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8840601444244385</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.69524747133255</v>
+        <v>0.5557493567466736</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6372659802436829</v>
+        <v>0.9994835257530212</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3926773071289062</v>
+        <v>0.4687929749488831</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7630854249000549</v>
+        <v>0.9999776482582092</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9689931273460388</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4610260128974915</v>
+        <v>0.4084399938583374</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6163369417190552</v>
+        <v>0.9999912977218628</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9678318500518799</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9514259696006775</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8544203042984009</v>
+        <v>0.9999969005584717</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7304010391235352</v>
+        <v>0.9987489581108093</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9329248070716858</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9661262035369873</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9529105424880981</v>
+        <v>0.9999985694885254</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9044431447982788</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2565562725067139</v>
+        <v>0.9893215894699097</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9708537459373474</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9649748802185059</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7420475482940674</v>
+        <v>0.3968373537063599</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9048248529434204</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9289169311523438</v>
+        <v>0.9984856247901917</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9621776342391968</v>
+        <v>0.9999997019767761</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5780013799667358</v>
+        <v>0.9680789113044739</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2739785313606262</v>
+        <v>0.2796128392219543</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8898189067840576</v>
+        <v>0.9830625653266907</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9259671568870544</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6748971939086914</v>
+        <v>0.8250868916511536</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8376629948616028</v>
+        <v>0.9893469214439392</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1708706617355347</v>
+        <v>0.3646167516708374</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7072519063949585</v>
+        <v>0.648526668548584</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5471808314323425</v>
+        <v>0.9952874183654785</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8551753163337708</v>
+        <v>0.6331233978271484</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8712447285652161</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8935849666595459</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6667560338973999</v>
+        <v>0.6444219350814819</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7963299155235291</v>
+        <v>0.9933255910873413</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.953804075717926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.632418155670166</v>
+        <v>0.5678763389587402</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8907746076583862</v>
+        <v>0.9999853372573853</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.02012646198272705</v>
+        <v>0.4786515235900879</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9103339910507202</v>
+        <v>0.9954788684844971</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6842058300971985</v>
+        <v>0.9492409825325012</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6369934678077698</v>
+        <v>0.9768797755241394</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1455458402633667</v>
+        <v>0.3532035350799561</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9293562173843384</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.445898175239563</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.5845574736595154</v>
+        <v>0.9904642105102539</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7140905261039734</v>
+        <v>0.6756708025932312</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1577112078666687</v>
+        <v>0.993902325630188</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.964714527130127</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3050634860992432</v>
+        <v>0.3456499576568604</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9094895720481873</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5194316506385803</v>
+        <v>0.5513766407966614</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7728552222251892</v>
+        <v>0.5005415678024292</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9517062306404114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9554732441902161</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8298839926719666</v>
+        <v>0.3493670225143433</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8261349201202393</v>
+        <v>0.9999979734420776</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8332823514938354</v>
+        <v>0.5358478426933289</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8657451272010803</v>
+        <v>0.9973660111427307</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9411430954933167</v>
+        <v>0.9999943971633911</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.9257025718688965</v>
+        <v>0.999829113483429</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9287473559379578</v>
+        <v>0.9999384880065918</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4325308799743652</v>
+        <v>0.4490759372711182</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4400296211242676</v>
+        <v>0.2987420558929443</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6069982051849365</v>
+        <v>0.3210474252700806</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1380116939544678</v>
+        <v>0.4252394437789917</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4111279845237732</v>
+        <v>0.582320511341095</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9539011716842651</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7279855012893677</v>
+        <v>0.4961915016174316</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8164682388305664</v>
+        <v>0.5552741885185242</v>
       </c>
     </row>
   </sheetData>

--- a/test_results_fold_final.xlsx
+++ b/test_results_fold_final.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5391277670860291</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6076937317848206</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9999997019767761</v>
+        <v>0.9854896664619446</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8661360740661621</v>
+        <v>0.9999627470970154</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9997403621673584</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9859791994094849</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9996679425239563</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5557493567466736</v>
+        <v>0.4697188138961792</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9994835257530212</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4687929749488831</v>
+        <v>0.9999997019767761</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9999776482582092</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4084399938583374</v>
+        <v>0.4437220096588135</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9999912977218628</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9999969005584717</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9987489581108093</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9999985694885254</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9999999403953552</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9893215894699097</v>
+        <v>0.5566455721855164</v>
       </c>
     </row>
     <row r="27">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9999999403953552</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3968373537063599</v>
+        <v>0.8470628261566162</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9984856247901917</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9999997019767761</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9680789113044739</v>
+        <v>0.5949496626853943</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2796128392219543</v>
+        <v>0.2456634044647217</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9830625653266907</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0.9503966569900513</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8250868916511536</v>
+        <v>0.999663233757019</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9893469214439392</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3646167516708374</v>
+        <v>0.2955101132392883</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.648526668548584</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9952874183654785</v>
+        <v>0.9171493649482727</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6331233978271484</v>
+        <v>0.4726004600524902</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0.9999979138374329</v>
       </c>
     </row>
     <row r="44">
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6444219350814819</v>
+        <v>0.5094053149223328</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9933255910873413</v>
+        <v>0.9995589852333069</v>
       </c>
     </row>
     <row r="47">
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5678763389587402</v>
+        <v>0.9994868040084839</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9999853372573853</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4786515235900879</v>
+        <v>0.3477116227149963</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9954788684844971</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9492409825325012</v>
+        <v>0.701953649520874</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9768797755241394</v>
+        <v>0.8666717410087585</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.3532035350799561</v>
+        <v>0.1886438131332397</v>
       </c>
     </row>
     <row r="55">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9999999403953552</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9904642105102539</v>
+        <v>0.9950524568557739</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6756708025932312</v>
+        <v>0.7549098134040833</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.993902325630188</v>
+        <v>0.714225172996521</v>
       </c>
     </row>
     <row r="60">
@@ -1102,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3456499576568604</v>
+        <v>0.2564208507537842</v>
       </c>
     </row>
     <row r="62">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5513766407966614</v>
+        <v>0.7959709763526917</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5005415678024292</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3493670225143433</v>
+        <v>0.6352491974830627</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9999979734420776</v>
+        <v>0.9999999403953552</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5358478426933289</v>
+        <v>0.9999969601631165</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9973660111427307</v>
+        <v>0.9638358950614929</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9999943971633911</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.999829113483429</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9999384880065918</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4490759372711182</v>
+        <v>0.5699102878570557</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2987420558929443</v>
+        <v>0.1839489340782166</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3210474252700806</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4252394437789917</v>
+        <v>0.3858974575996399</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.582320511341095</v>
+        <v>0.9923981428146362</v>
       </c>
     </row>
     <row r="79">
@@ -1311,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4961915016174316</v>
+        <v>0.3294940590858459</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0.5552741885185242</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/test_results_fold_final.xlsx
+++ b/test_results_fold_final.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.4923528432846069</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +464,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.5207343101501465</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9854896664619446</v>
+        <v>0.9999220371246338</v>
       </c>
     </row>
     <row r="5">
@@ -486,7 +486,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9999627470970154</v>
+        <v>0.9929780960083008</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.9952062964439392</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.9983266592025757</v>
       </c>
     </row>
     <row r="8">
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.9995290040969849</v>
       </c>
     </row>
     <row r="9">
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.9999973773956299</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0.9994825720787048</v>
       </c>
     </row>
     <row r="11">
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4697188138961792</v>
+        <v>0.4302995800971985</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0.9738502502441406</v>
       </c>
     </row>
     <row r="13">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9999997019767761</v>
+        <v>0.3967447876930237</v>
       </c>
     </row>
     <row r="14">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0.9972354769706726</v>
       </c>
     </row>
     <row r="15">
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0.999987006187439</v>
       </c>
     </row>
     <row r="16">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4437220096588135</v>
+        <v>0.2665575742721558</v>
       </c>
     </row>
     <row r="17">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.9880098700523376</v>
       </c>
     </row>
     <row r="18">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.9999707341194153</v>
       </c>
     </row>
     <row r="19">
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.9999975562095642</v>
       </c>
     </row>
     <row r="20">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.9999417066574097</v>
       </c>
     </row>
     <row r="21">
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.9951073527336121</v>
       </c>
     </row>
     <row r="22">
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.9999057054519653</v>
       </c>
     </row>
     <row r="23">
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.9996277689933777</v>
       </c>
     </row>
     <row r="24">
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.9997483491897583</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0.9995420575141907</v>
       </c>
     </row>
     <row r="26">
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5566455721855164</v>
+        <v>0.3030815124511719</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.9999971985816956</v>
       </c>
     </row>
     <row r="28">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.9998877644538879</v>
       </c>
     </row>
     <row r="29">
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8470628261566162</v>
+        <v>0.731154203414917</v>
       </c>
     </row>
     <row r="30">
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.9999528527259827</v>
       </c>
     </row>
     <row r="31">
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0.9923992156982422</v>
       </c>
     </row>
     <row r="32">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0.9999678134918213</v>
       </c>
     </row>
     <row r="33">
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5949496626853943</v>
+        <v>0.9731897711753845</v>
       </c>
     </row>
     <row r="34">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2456634044647217</v>
+        <v>0.1883106231689453</v>
       </c>
     </row>
     <row r="35">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0.8482128381729126</v>
       </c>
     </row>
     <row r="36">
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9503966569900513</v>
+        <v>0.9999740123748779</v>
       </c>
     </row>
     <row r="37">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.999663233757019</v>
+        <v>0.4354331493377686</v>
       </c>
     </row>
     <row r="38">
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0.8814858198165894</v>
       </c>
     </row>
     <row r="39">
@@ -860,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2955101132392883</v>
+        <v>0.1883244514465332</v>
       </c>
     </row>
     <row r="40">
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0.7942331433296204</v>
       </c>
     </row>
     <row r="41">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9171493649482727</v>
+        <v>0.9991356134414673</v>
       </c>
     </row>
     <row r="42">
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4726004600524902</v>
+        <v>0.4700289964675903</v>
       </c>
     </row>
     <row r="43">
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9999979138374329</v>
+        <v>0.9995539784431458</v>
       </c>
     </row>
     <row r="44">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0.9997694492340088</v>
       </c>
     </row>
     <row r="45">
@@ -926,7 +926,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5094053149223328</v>
+        <v>0.5567795038223267</v>
       </c>
     </row>
     <row r="46">
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9995589852333069</v>
+        <v>0.9858752489089966</v>
       </c>
     </row>
     <row r="47">
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0.9999961256980896</v>
       </c>
     </row>
     <row r="48">
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9994868040084839</v>
+        <v>0.6056366562843323</v>
       </c>
     </row>
     <row r="49">
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0.9931397438049316</v>
       </c>
     </row>
     <row r="50">
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3477116227149963</v>
+        <v>0.4239267110824585</v>
       </c>
     </row>
     <row r="51">
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9999999403953552</v>
+        <v>0.9800018072128296</v>
       </c>
     </row>
     <row r="52">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.701953649520874</v>
+        <v>0.5309568643569946</v>
       </c>
     </row>
     <row r="53">
@@ -1014,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8666717410087585</v>
+        <v>0.9999409914016724</v>
       </c>
     </row>
     <row r="54">
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1886438131332397</v>
+        <v>0.2553474903106689</v>
       </c>
     </row>
     <row r="55">
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0.9999825358390808</v>
       </c>
     </row>
     <row r="56">
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>0.993938684463501</v>
       </c>
     </row>
     <row r="57">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9950524568557739</v>
+        <v>0.9993432760238647</v>
       </c>
     </row>
     <row r="58">
@@ -1069,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>0.7549098134040833</v>
+        <v>0.5054194331169128</v>
       </c>
     </row>
     <row r="59">
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.714225172996521</v>
+        <v>0.6266266107559204</v>
       </c>
     </row>
     <row r="60">
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0.9996373653411865</v>
       </c>
     </row>
     <row r="61">
@@ -1102,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2564208507537842</v>
+        <v>0.2674463987350464</v>
       </c>
     </row>
     <row r="62">
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0.9999717473983765</v>
       </c>
     </row>
     <row r="63">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7959709763526917</v>
+        <v>0.5085382461547852</v>
       </c>
     </row>
     <row r="64">
@@ -1135,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0.5907906889915466</v>
       </c>
     </row>
     <row r="65">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>0.9999971985816956</v>
       </c>
     </row>
     <row r="66">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>0.9998382329940796</v>
       </c>
     </row>
     <row r="67">
@@ -1168,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6352491974830627</v>
+        <v>0.7272596955299377</v>
       </c>
     </row>
     <row r="68">
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9999999403953552</v>
+        <v>0.9997031092643738</v>
       </c>
     </row>
     <row r="69">
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9999969601631165</v>
+        <v>0.9970119595527649</v>
       </c>
     </row>
     <row r="70">
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9638358950614929</v>
+        <v>0.9920804500579834</v>
       </c>
     </row>
     <row r="71">
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0.9999731183052063</v>
       </c>
     </row>
     <row r="72">
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0.9997006058692932</v>
       </c>
     </row>
     <row r="73">
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>0.9998795390129089</v>
       </c>
     </row>
     <row r="74">
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5699102878570557</v>
+        <v>0.4821646213531494</v>
       </c>
     </row>
     <row r="75">
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.1839489340782166</v>
+        <v>0.5215715169906616</v>
       </c>
     </row>
     <row r="76">
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0.4384623169898987</v>
       </c>
     </row>
     <row r="77">
@@ -1278,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3858974575996399</v>
+        <v>0.4380652904510498</v>
       </c>
     </row>
     <row r="78">
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0.9923981428146362</v>
+        <v>0.4235278964042664</v>
       </c>
     </row>
     <row r="79">
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0.9999983906745911</v>
       </c>
     </row>
     <row r="80">
@@ -1311,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3294940590858459</v>
+        <v>0.4956464171409607</v>
       </c>
     </row>
     <row r="81">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0.8230998516082764</v>
       </c>
     </row>
   </sheetData>
